--- a/output/pdf_financials_xlsx/TLRY.xlsx
+++ b/output/pdf_financials_xlsx/TLRY.xlsx
@@ -2657,13 +2657,13 @@
         <v>48.92</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>46.786</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>37.722</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>31.332</v>
+        <v>31.406</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -4846,13 +4846,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.261589</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.723903</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.723903</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19100,7 +19100,11 @@
           <t>Share-based payment reserve 23 3,229,929</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -20394,7 +20398,11 @@
           <t>Share-based payment reserve 18</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -21640,7 +21648,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
